--- a/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/501/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,110 +626,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
-</t>
+          <t>355</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="U4" s="2" t="n"/>
@@ -752,141 +734,118 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5127
-</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1360
-</t>
+          <t>360</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -903,141 +862,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5048
-</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20239
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1054,8 +990,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5836
-</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1065,134 +1000,112 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">424
-</t>
+          <t>424</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1209,135 +1122,113 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4851
-</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1359,146 +1250,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26361
-</t>
+          <t>26560</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
-</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11134
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">442
-</t>
+          <t>442</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">684
-</t>
+          <t>684</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
-</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11830
-</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">487
-</t>
+          <t>497</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248
-</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1367
-</t>
+          <t>367</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1515,136 +1382,114 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5312
-</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N10" s="2" t="n"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
-</t>
+          <t>389</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11062
-</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,104 +1506,87 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4279
-</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1768,8 +1596,7 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="V11" s="2" t="n"/>
@@ -1791,8 +1618,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2067
-</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1803,74 +1629,62 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1880,50 +1694,42 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,14 +1746,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6013
-</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">343
-</t>
+          <t>343</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1957,123 +1761,103 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>392</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2090,141 +1874,118 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4880
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2241,141 +2002,118 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5529
-</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4180
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2392,146 +2130,122 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2377
-</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129 16
-</t>
+          <t>159 6</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">768
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21182
-</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
-</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3973
-</t>
+          <t>353</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
-</t>
+          <t>362</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8809
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
-</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1547
-</t>
+          <t>1547</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1736
-</t>
+          <t>736</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">483
-</t>
+          <t>483</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11458
-</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2548,146 +2262,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3154
-</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
+          <t>425</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
-</t>
+          <t>376</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2704,141 +2394,118 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2521
-</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>375</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2855,146 +2522,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3264
-</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">414
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3021,134 +2664,112 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,140 +2786,117 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3320,123 +2918,103 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5363
-</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">020
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
@@ -3446,14 +3024,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3470,141 +3046,118 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25175
-</t>
+          <t>25475</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1603
-</t>
+          <t>1603</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1171
-</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
-</t>
+          <t>868</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
-</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1544
-</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">366
-</t>
+          <t>366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1872
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
-</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1428
-</t>
+          <t>428</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3621,141 +3174,118 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2946
-</t>
+          <t>546</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>011</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3772,146 +3302,122 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">400
-</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4573
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3928,146 +3434,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5304
-</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4084,146 +3566,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501
-</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4240,140 +3698,117 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6210
-</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5984
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">934
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -4395,122 +3830,102 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6249
-</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2383
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">413
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1471
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4520,20 +3935,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4550,128 +3962,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27819
-</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
-</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
-</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">871
-</t>
+          <t>871</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">570
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
-</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>517</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
-</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1941
-</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr"/>
@@ -4682,8 +4073,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4700,130 +4090,109 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3364
-</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">465
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr"/>
@@ -4841,105 +4210,88 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2086
-</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">338
-</t>
+          <t>338</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>390</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">336
-</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4949,14 +4301,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr"/>
@@ -4984,146 +4334,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4437
-</t>
+          <t>2437</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14209
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5140,14 +4466,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3866
-</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -5157,128 +4481,107 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5295,50 +4598,42 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339
-</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -5348,92 +4643,77 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1589
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">334
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5450,8 +4730,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3413
-</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5461,129 +4740,108 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1048
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>540</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
-</t>
+          <t>348</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1806
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1466
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5600,141 +4858,118 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22166
-</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1103
-</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">827
-</t>
+          <t>827</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
-</t>
+          <t>358</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
-</t>
+          <t>532</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">447
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24092
-</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
+          <t>393</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1478
-</t>
+          <t>479</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
-</t>
+          <t>1516</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1340
-</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11411
-</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5751,141 +4986,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433
-</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">374
-</t>
+          <t>374</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5902,146 +5118,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59146
-</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11580
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
-</t>
+          <t>364</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6058,146 +5250,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6171
-</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12680
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3180
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6214,14 +5382,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5875
-</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6231,128 +5397,107 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6369,80 +5514,67 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4811
-</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">500
-</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -6452,62 +5584,52 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13920
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6524,146 +5646,122 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2340
-</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6680,146 +5778,122 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2580
-</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
-</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">092
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6440
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12279
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2908
-</t>
+          <t>508</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6836,14 +5910,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23122
-</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>1857</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -6853,111 +5925,93 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9108
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71949
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12029
-</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
-</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29084
-</t>
+          <t>584</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1780
-</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1369
-</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1826
-</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1647
-</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr"/>
@@ -6976,141 +6030,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518
-</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4706
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1494
-</t>
+          <t>494</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1390
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23908
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
